--- a/data/valuations/PLAY/PLAY_modelo_valoracion.xlsx
+++ b/data/valuations/PLAY/PLAY_modelo_valoracion.xlsx
@@ -638,19 +638,19 @@
         </is>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.0009999999999999992</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.029</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.019</v>
+        <v>0.049</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.029</v>
+        <v>0.05</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.03900000000000001</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="9">
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.019</v>
+        <v>0.004</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.0171</v>
+        <v>0.0036</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.0152</v>
+        <v>0.0032</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.0133</v>
+        <v>0.0028</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.0114</v>
+        <v>0.0024</v>
       </c>
     </row>
     <row r="10">
@@ -682,19 +682,19 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.03099999999999999</v>
+        <v>-0.005999999999999998</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.02099999999999999</v>
+        <v>0.014</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.011</v>
+        <v>0.034</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-0.0009999999999999939</v>
+        <v>0.05</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.009000000000000008</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="11">
@@ -797,19 +797,19 @@
         </is>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.8627129497765708</v>
+        <v>0.8527129497765707</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.8627129497765708</v>
+        <v>0.8527129497765707</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.8627129497765708</v>
+        <v>0.8527129497765707</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.8627129497765708</v>
+        <v>0.8527129497765707</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.8627129497765708</v>
+        <v>0.8527129497765707</v>
       </c>
     </row>
     <row r="17">
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.8227129497765707</v>
+        <v>0.8327129497765707</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.8227129497765707</v>
+        <v>0.8327129497765707</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.8227129497765707</v>
+        <v>0.8327129497765707</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.8227129497765707</v>
+        <v>0.8327129497765707</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.8227129497765707</v>
+        <v>0.8327129497765707</v>
       </c>
     </row>
     <row r="18">
@@ -868,19 +868,19 @@
         </is>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.2924041431015079</v>
+        <v>0.6395901476947027</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.2924041431015079</v>
+        <v>0.6395901476947027</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.2924041431015079</v>
+        <v>0.6395901476947027</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.2924041431015079</v>
+        <v>0.6395901476947027</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.2924041431015079</v>
+        <v>0.6395901476947027</v>
       </c>
     </row>
     <row r="21">
@@ -890,19 +890,19 @@
         </is>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.2824041431015079</v>
+        <v>0.6345901476947027</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.2824041431015079</v>
+        <v>0.6345901476947027</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.2824041431015079</v>
+        <v>0.6345901476947027</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.2824041431015079</v>
+        <v>0.6345901476947027</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.2824041431015079</v>
+        <v>0.6345901476947027</v>
       </c>
     </row>
     <row r="22">
@@ -912,19 +912,19 @@
         </is>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.3024041431015079</v>
+        <v>0.6445901476947027</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.3024041431015079</v>
+        <v>0.6445901476947027</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.3024041431015079</v>
+        <v>0.6445901476947027</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.3024041431015079</v>
+        <v>0.6445901476947027</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.3024041431015079</v>
+        <v>0.6445901476947027</v>
       </c>
     </row>
     <row r="23">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -983,19 +983,19 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.1470657314709076</v>
+        <v>0.1344761748928229</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.1470657314709076</v>
+        <v>0.1344761748928229</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.1470657314709076</v>
+        <v>0.1344761748928229</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.1470657314709076</v>
+        <v>0.1344761748928229</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.1470657314709076</v>
+        <v>0.1344761748928229</v>
       </c>
     </row>
     <row r="32">
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0.0515</v>
+        <v>0.0592</v>
       </c>
     </row>
     <row r="36">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.0415</v>
+        <v>0.0492</v>
       </c>
     </row>
     <row r="37">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.0692</v>
       </c>
     </row>
     <row r="38">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41">
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="C41" s="9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43">
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="F2" s="16" t="n">
-        <v>13.76</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="4">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="K21" s="8">
-        <f>K12*$C$16</f>
+        <f>K8*$C$16</f>
         <v/>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="C34" s="20">
-        <f>C33/13.76-1</f>
+        <f>C33/9.81-1</f>
         <v/>
       </c>
     </row>
@@ -3727,202 +3727,202 @@
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>8x</t>
+          <t>10x</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>10x</t>
+          <t>12x</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>12x</t>
+          <t>14x</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>14x</t>
+          <t>16x</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>16x</t>
+          <t>18x</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="21" t="n">
-        <v>0.0215</v>
+        <v>0.0292</v>
       </c>
       <c r="C39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*8/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*10/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*10/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*12/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*12/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*14/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*14/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*16/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*16/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*18/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="21" t="n">
-        <v>0.0315</v>
+        <v>0.0392</v>
       </c>
       <c r="C40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*8/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*10/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*10/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*12/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*12/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*14/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*14/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*16/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*16/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*18/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="n">
-        <v>0.0415</v>
+        <v>0.0492</v>
       </c>
       <c r="C41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*8/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*10/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*10/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*12/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*12/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*14/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*14/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*16/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*16/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*18/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="21" t="n">
-        <v>0.0515</v>
+        <v>0.0592</v>
       </c>
       <c r="C42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*8/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*10/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*10/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*12/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E42" s="23">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*12/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*14/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*14/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*16/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*16/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*18/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="n">
-        <v>0.0615</v>
+        <v>0.0692</v>
       </c>
       <c r="C43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*8/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*10/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*10/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*12/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*12/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*14/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*14/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*16/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*16/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*18/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="21" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="C44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*8/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*10/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*10/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*12/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*12/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*14/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*14/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*16/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*16/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*18/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="21" t="n">
-        <v>0.08149999999999999</v>
+        <v>0.0892</v>
       </c>
       <c r="C45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*8/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*10/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*10/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*12/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*12/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*14/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*14/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*16/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*16/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*18/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>

--- a/data/valuations/PLAY/PLAY_modelo_valoracion.xlsx
+++ b/data/valuations/PLAY/PLAY_modelo_valoracion.xlsx
@@ -551,47 +551,47 @@
     <row r="4">
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2026</t>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY2027</t>
         </is>
       </c>
       <c r="H4" s="1" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY2028</t>
         </is>
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
-          <t>FY2028</t>
+          <t>FY2029</t>
         </is>
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>FY2029</t>
+          <t>FY2030</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>FY2030</t>
+          <t>FY2031</t>
         </is>
       </c>
     </row>
@@ -619,16 +619,16 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1304</v>
+        <v>1964.4</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1964.4</v>
+        <v>2205.3</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>2205.3</v>
+        <v>2132.7</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>2132.7</v>
+        <v>2102.8</v>
       </c>
     </row>
     <row r="8">
@@ -638,13 +638,13 @@
         </is>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.011</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.029</v>
+        <v>0.031</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.049</v>
+        <v>0.05</v>
       </c>
       <c r="J8" s="6" t="n">
         <v>0.05</v>
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="H9" s="6" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="K9" s="6" t="n">
         <v>0.0036</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="J9" s="6" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>0.0024</v>
       </c>
     </row>
     <row r="10">
@@ -682,13 +682,13 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.005999999999999998</v>
+        <v>-0.004</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.014</v>
+        <v>0.016</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.034</v>
+        <v>0.036</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>0.05</v>
@@ -775,19 +775,19 @@
         </is>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.8427129497765707</v>
+        <v>0.8462935284324323</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.8427129497765707</v>
+        <v>0.8462935284324323</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.8427129497765707</v>
+        <v>0.8462935284324323</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.8427129497765707</v>
+        <v>0.8462935284324323</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.8427129497765707</v>
+        <v>0.8462935284324323</v>
       </c>
     </row>
     <row r="16">
@@ -797,19 +797,19 @@
         </is>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.8527129497765707</v>
+        <v>0.8562935284324323</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.8527129497765707</v>
+        <v>0.8562935284324323</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.8527129497765707</v>
+        <v>0.8562935284324323</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.8527129497765707</v>
+        <v>0.8562935284324323</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.8527129497765707</v>
+        <v>0.8562935284324323</v>
       </c>
     </row>
     <row r="17">
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.8327129497765707</v>
+        <v>0.8362935284324323</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.8327129497765707</v>
+        <v>0.8362935284324323</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.8327129497765707</v>
+        <v>0.8362935284324323</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.8327129497765707</v>
+        <v>0.8362935284324323</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.8327129497765707</v>
+        <v>0.8362935284324323</v>
       </c>
     </row>
     <row r="18">
@@ -868,19 +868,19 @@
         </is>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.6395901476947027</v>
+        <v>0.796312550688472</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.6395901476947027</v>
+        <v>0.796312550688472</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.6395901476947027</v>
+        <v>0.796312550688472</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.6395901476947027</v>
+        <v>0.796312550688472</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.6395901476947027</v>
+        <v>0.796312550688472</v>
       </c>
     </row>
     <row r="21">
@@ -890,19 +890,19 @@
         </is>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.6345901476947027</v>
+        <v>0.7913125506884719</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.6345901476947027</v>
+        <v>0.7913125506884719</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.6345901476947027</v>
+        <v>0.7913125506884719</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.6345901476947027</v>
+        <v>0.7913125506884719</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.6345901476947027</v>
+        <v>0.7913125506884719</v>
       </c>
     </row>
     <row r="22">
@@ -912,19 +912,19 @@
         </is>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.6445901476947027</v>
+        <v>0.801312550688472</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.6445901476947027</v>
+        <v>0.801312550688472</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.6445901476947027</v>
+        <v>0.801312550688472</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.6445901476947027</v>
+        <v>0.801312550688472</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.6445901476947027</v>
+        <v>0.801312550688472</v>
       </c>
     </row>
     <row r="23">
@@ -1054,19 +1054,19 @@
         </is>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.09961918160843779</v>
+        <v>0.1063222256653832</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.09961918160843779</v>
+        <v>0.1063222256653832</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.09961918160843779</v>
+        <v>0.1063222256653832</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.09961918160843779</v>
+        <v>0.1063222256653832</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.09961918160843779</v>
+        <v>0.1063222256653832</v>
       </c>
     </row>
     <row r="31">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.1344761748928229</v>
+        <v>0.1679314853927093</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.1344761748928229</v>
+        <v>0.1679314853927093</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.1344761748928229</v>
+        <v>0.1679314853927093</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.1344761748928229</v>
+        <v>0.1679314853927093</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.1344761748928229</v>
+        <v>0.1679314853927093</v>
       </c>
     </row>
     <row r="32">
@@ -1098,19 +1098,19 @@
         </is>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.09722687687472092</v>
+        <v>0.1185761100191721</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.09722687687472092</v>
+        <v>0.1185761100191721</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.09722687687472092</v>
+        <v>0.1185761100191721</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.09722687687472092</v>
+        <v>0.1185761100191721</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.09722687687472092</v>
+        <v>0.1185761100191721</v>
       </c>
     </row>
     <row r="34">
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0.0592</v>
+        <v>0.1038</v>
       </c>
     </row>
     <row r="36">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.0492</v>
+        <v>0.09380000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.0692</v>
+        <v>0.1138</v>
       </c>
     </row>
     <row r="38">
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2026</t>
         </is>
       </c>
     </row>
@@ -1298,16 +1298,16 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1304</v>
+        <v>1964.4</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>1964.4</v>
+        <v>2205.3</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>2205.3</v>
+        <v>2132.7</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>2132.7</v>
+        <v>2102.8</v>
       </c>
     </row>
     <row r="7">
@@ -1317,16 +1317,16 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>204.9</v>
+        <v>323.2</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>323.2</v>
+        <v>353</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>353</v>
+        <v>314.4</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>314.4</v>
+        <v>300.3</v>
       </c>
     </row>
     <row r="8">
@@ -1336,16 +1336,16 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1099.1</v>
+        <v>1641.2</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>1641.2</v>
+        <v>1852.3</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1852.3</v>
+        <v>1818.3</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>1818.3</v>
+        <v>1802.5</v>
       </c>
     </row>
     <row r="9">
@@ -1355,16 +1355,16 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>0.8428680981595092</v>
+        <v>0.835471390755447</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>0.835471390755447</v>
+        <v>0.8399310751371696</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>0.8399310751371696</v>
+        <v>0.8525812350541567</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.8525812350541567</v>
+        <v>0.857190412782956</v>
       </c>
     </row>
     <row r="11">
@@ -1393,16 +1393,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>362.8</v>
+        <v>607.4</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>607.4</v>
+        <v>639.7</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>639.7</v>
+        <v>623</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>623</v>
+        <v>652.8</v>
       </c>
     </row>
     <row r="13">
@@ -1412,16 +1412,16 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>195.3</v>
+        <v>277.1</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>277.1</v>
+        <v>325</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>325</v>
+        <v>239.1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>239.1</v>
+        <v>105.1</v>
       </c>
     </row>
     <row r="14">
@@ -1431,16 +1431,16 @@
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>0.1497699386503067</v>
+        <v>0.1410608837304011</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>0.1410608837304011</v>
+        <v>0.147372239604589</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>0.147372239604589</v>
+        <v>0.112111408074272</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>0.112111408074272</v>
+        <v>0.04998097774396043</v>
       </c>
     </row>
     <row r="16">
@@ -1450,16 +1450,16 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>49.7</v>
+        <v>79.5</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>79.5</v>
+        <v>120.3</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>120.3</v>
+        <v>125.1</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>125.1</v>
+        <v>145.7</v>
       </c>
     </row>
     <row r="17">
@@ -1469,16 +1469,16 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>19</v>
+        <v>36.5</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>36.5</v>
+        <v>36.2</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>36.2</v>
+        <v>11.6</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>11.6</v>
+        <v>-19.2</v>
       </c>
     </row>
     <row r="18">
@@ -1488,16 +1488,16 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>108.7</v>
+        <v>137.1</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>137.1</v>
+        <v>126.9</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>126.9</v>
+        <v>58.3</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>58.3</v>
+        <v>-48.7</v>
       </c>
     </row>
     <row r="19">
@@ -1507,16 +1507,16 @@
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>0.08335889570552148</v>
+        <v>0.06979230299328039</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>0.06979230299328039</v>
+        <v>0.05754319140253027</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.05754319140253027</v>
+        <v>0.02733624044638252</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.02733624044638252</v>
+        <v>-0.02315959672817196</v>
       </c>
     </row>
     <row r="21">
@@ -1526,16 +1526,16 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>315.7</v>
+        <v>422.4</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>422.4</v>
+        <v>491.9</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>491.9</v>
+        <v>433.2</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>433.2</v>
+        <v>357.2</v>
       </c>
     </row>
     <row r="22">
@@ -1545,16 +1545,16 @@
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>0.242101226993865</v>
+        <v>0.2150274893097129</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>0.2150274893097129</v>
+        <v>0.2230535528046071</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.2230535528046071</v>
+        <v>0.2031228020818681</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.2031228020818681</v>
+        <v>0.169868746433327</v>
       </c>
     </row>
     <row r="23">
@@ -1564,16 +1564,16 @@
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>2.21</v>
+        <v>2.79</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>2.88</v>
+        <v>1.46</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>1.46</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="24">
@@ -1583,16 +1583,16 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>138.3</v>
+        <v>169.3</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>169.3</v>
+        <v>208.5</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>208.5</v>
+        <v>238.2</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>238.2</v>
+        <v>279.4</v>
       </c>
     </row>
     <row r="27">
@@ -1614,16 +1614,16 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>25.91</v>
+        <v>181.6</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>181.6</v>
+        <v>37.3</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>37.3</v>
+        <v>6.9</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>6.9</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="29">
@@ -1633,16 +1633,16 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>145.571</v>
+        <v>293.7</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>293.7</v>
+        <v>137.5</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>137.5</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>94.40000000000001</v>
+        <v>124.1</v>
       </c>
     </row>
     <row r="30">
@@ -1652,16 +1652,16 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>1815.794</v>
+        <v>2513.8</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>2513.8</v>
+        <v>2656</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>2656</v>
+        <v>2953</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>2953</v>
+        <v>3022.2</v>
       </c>
     </row>
     <row r="31">
@@ -1671,13 +1671,13 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>272.597</v>
+        <v>744.5</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>744.5</v>
+        <v>742.5</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>742.5</v>
+        <v>742.6</v>
       </c>
       <c r="F31" s="5" t="n">
         <v>742.6</v>
@@ -1690,16 +1690,16 @@
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>2345.79</v>
+        <v>3761</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>3761</v>
+        <v>3754.4</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>3754.4</v>
+        <v>4015.8</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>4015.8</v>
+        <v>4116.6</v>
       </c>
     </row>
     <row r="34">
@@ -1709,16 +1709,16 @@
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>311.515</v>
+        <v>438</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>438</v>
+        <v>435.6</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>435.6</v>
+        <v>433.9</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>433.9</v>
+        <v>434.6</v>
       </c>
     </row>
     <row r="35">
@@ -1728,16 +1728,16 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>1754.379</v>
+        <v>2863.1</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>2863.1</v>
+        <v>2914.6</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>2914.6</v>
+        <v>3139</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>3139</v>
+        <v>3165.1</v>
       </c>
     </row>
     <row r="36">
@@ -1747,16 +1747,16 @@
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>2070.33</v>
+        <v>3350.5</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>3350.5</v>
+        <v>3503.2</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>3503.2</v>
+        <v>3870</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>3870</v>
+        <v>4025.4</v>
       </c>
     </row>
     <row r="38">
@@ -1766,16 +1766,16 @@
         </is>
       </c>
       <c r="C38" s="5" t="n">
-        <v>275.46</v>
+        <v>410.5</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>410.5</v>
+        <v>251.2</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>251.2</v>
+        <v>145.8</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>145.8</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="41">
@@ -1797,16 +1797,16 @@
         </is>
       </c>
       <c r="C42" s="5" t="n">
-        <v>283.2</v>
+        <v>444.4</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>444.4</v>
+        <v>364.2</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>364.2</v>
+        <v>312.3</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>312.3</v>
+        <v>290.8</v>
       </c>
     </row>
     <row r="43">
@@ -1816,16 +1816,16 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>-92.2</v>
+        <v>-234.2</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>-234.2</v>
+        <v>-330.2</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>-330.2</v>
+        <v>-530.2</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>-530.2</v>
+        <v>-391.4</v>
       </c>
     </row>
     <row r="44">
@@ -1835,16 +1835,16 @@
         </is>
       </c>
       <c r="C44" s="5" t="n">
-        <v>191</v>
+        <v>210.2</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>210.2</v>
+        <v>34</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>34</v>
+        <v>-217.9</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>-217.9</v>
+        <v>-100.6</v>
       </c>
     </row>
     <row r="46">
@@ -1854,16 +1854,16 @@
         </is>
       </c>
       <c r="C46" s="5" t="n">
-        <v>138.3</v>
+        <v>169.3</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>169.3</v>
+        <v>208.5</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>208.5</v>
+        <v>238.2</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>238.2</v>
+        <v>279.4</v>
       </c>
     </row>
     <row r="47">
@@ -1873,16 +1873,16 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>16</v>
+        <v>4.6</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>4.6</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="48">
@@ -1892,16 +1892,16 @@
         </is>
       </c>
       <c r="C48" s="5" t="n">
-        <v>11.8</v>
+        <v>73.2</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>73.2</v>
+        <v>-40.5</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>-40.5</v>
+        <v>-28.7</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>-28.7</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -1968,47 +1968,47 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2026</t>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY2027</t>
         </is>
       </c>
       <c r="H4" s="1" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY2028</t>
         </is>
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
-          <t>FY2028</t>
+          <t>FY2029</t>
         </is>
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>FY2029</t>
+          <t>FY2030</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>FY2030</t>
+          <t>FY2031</t>
         </is>
       </c>
     </row>
@@ -2063,16 +2063,16 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1304</v>
+        <v>1964.4</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>1964.4</v>
+        <v>2205.3</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>2205.3</v>
+        <v>2132.7</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>2132.7</v>
+        <v>2102.8</v>
       </c>
       <c r="G8" s="8">
         <f>Assumptions!G12</f>
@@ -2283,16 +2283,16 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>204.9</v>
+        <v>323.2</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>323.2</v>
+        <v>353</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>353</v>
+        <v>314.4</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>314.4</v>
+        <v>300.3</v>
       </c>
       <c r="G16" s="8">
         <f>-G15*(1-Assumptions!G18)</f>
@@ -2408,16 +2408,16 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>362.8</v>
+        <v>607.4</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>607.4</v>
+        <v>639.7</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>639.7</v>
+        <v>623</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>623</v>
+        <v>652.8</v>
       </c>
       <c r="G20" s="8">
         <f>-G15*Assumptions!G24</f>
@@ -2486,16 +2486,16 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>138.3</v>
+        <v>169.3</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>169.3</v>
+        <v>208.5</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>208.5</v>
+        <v>238.2</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>238.2</v>
+        <v>279.4</v>
       </c>
       <c r="G22" s="8">
         <f>-G15*Assumptions!G32</f>
@@ -2697,31 +2697,31 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>49.7</v>
+        <v>79.5</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>79.5</v>
+        <v>120.3</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>120.3</v>
+        <v>125.1</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>125.1</v>
+        <v>145.7</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>125.1</v>
+        <v>145.7</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>125.1</v>
+        <v>145.7</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>125.1</v>
+        <v>145.7</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>125.1</v>
+        <v>145.7</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>125.1</v>
+        <v>145.7</v>
       </c>
     </row>
     <row r="30">
@@ -2774,16 +2774,16 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>19</v>
+        <v>36.5</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>36.5</v>
+        <v>36.2</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>36.2</v>
+        <v>11.6</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>11.6</v>
+        <v>-19.2</v>
       </c>
       <c r="G31" s="8">
         <f>-ABS(G30)*Assumptions!G34</f>
@@ -3002,16 +3002,16 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>11.8</v>
+        <v>73.2</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>73.2</v>
+        <v>-40.5</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>-40.5</v>
+        <v>-28.7</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>-28.7</v>
+        <v>7.9</v>
       </c>
       <c r="G39" s="5" t="n">
         <v>0</v>
@@ -3079,16 +3079,16 @@
         </is>
       </c>
       <c r="C42" s="5" t="n">
-        <v>-92.2</v>
+        <v>-234.2</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>-234.2</v>
+        <v>-330.2</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>-330.2</v>
+        <v>-530.2</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>-530.2</v>
+        <v>-391.4</v>
       </c>
       <c r="G42" s="8">
         <f>-ABS(G15)*Assumptions!G33</f>
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="F2" s="16" t="n">
-        <v>9.81</v>
+        <v>12.35</v>
       </c>
     </row>
     <row r="4">
@@ -3295,19 +3295,19 @@
         </is>
       </c>
       <c r="G4" s="1" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>2030</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="5">
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C29" s="18" t="n">
-        <v>-3132.1</v>
+        <v>-3148.5</v>
       </c>
     </row>
     <row r="30">
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="C34" s="20">
-        <f>C33/9.81-1</f>
+        <f>C33/12.35-1</f>
         <v/>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
     </row>
     <row r="39">
       <c r="A39" s="21" t="n">
-        <v>0.0292</v>
+        <v>0.0738</v>
       </c>
       <c r="C39" s="22">
         <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*10/(1+$A$39)^5+$C$29)/$C$32</f>
@@ -3778,7 +3778,7 @@
     </row>
     <row r="40">
       <c r="A40" s="21" t="n">
-        <v>0.0392</v>
+        <v>0.0838</v>
       </c>
       <c r="C40" s="22">
         <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*10/(1+$A$40)^5+$C$29)/$C$32</f>
@@ -3803,7 +3803,7 @@
     </row>
     <row r="41">
       <c r="A41" s="21" t="n">
-        <v>0.0492</v>
+        <v>0.09380000000000001</v>
       </c>
       <c r="C41" s="22">
         <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*10/(1+$A$41)^5+$C$29)/$C$32</f>
@@ -3828,7 +3828,7 @@
     </row>
     <row r="42">
       <c r="A42" s="21" t="n">
-        <v>0.0592</v>
+        <v>0.1038</v>
       </c>
       <c r="C42" s="22">
         <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*10/(1+$A$42)^5+$C$29)/$C$32</f>
@@ -3853,7 +3853,7 @@
     </row>
     <row r="43">
       <c r="A43" s="21" t="n">
-        <v>0.0692</v>
+        <v>0.1138</v>
       </c>
       <c r="C43" s="22">
         <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*10/(1+$A$43)^5+$C$29)/$C$32</f>
@@ -3878,7 +3878,7 @@
     </row>
     <row r="44">
       <c r="A44" s="21" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.1238</v>
       </c>
       <c r="C44" s="22">
         <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*10/(1+$A$44)^5+$C$29)/$C$32</f>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="45">
       <c r="A45" s="21" t="n">
-        <v>0.0892</v>
+        <v>0.1338</v>
       </c>
       <c r="C45" s="22">
         <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*10/(1+$A$45)^5+$C$29)/$C$32</f>
